--- a/Data/Excel/Enum/Enum.xlsx
+++ b/Data/Excel/Enum/Enum.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitWorks\GameServerStudyAspNet\Data\Excel\Enum\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{075A9818-95FD-46B7-B85A-A7B6C53245F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC357BF4-800D-4E53-9CCC-DF0B6749A210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{B14C0FCD-ADAC-43B5-88EF-CD027C78C01B}"/>
+    <workbookView xWindow="1110" yWindow="1725" windowWidth="24975" windowHeight="11295" activeTab="3" xr2:uid="{B14C0FCD-ADAC-43B5-88EF-CD027C78C01B}"/>
   </bookViews>
   <sheets>
     <sheet name="Common" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="114">
   <si>
     <t>#</t>
   </si>
@@ -465,6 +465,21 @@
   <si>
     <t>SERVER_DOWN</t>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>EErrorCode</t>
+  </si>
+  <si>
+    <t>SESSION_NOT_FOUND</t>
+  </si>
+  <si>
+    <t>SESSION_EXPIRED</t>
+  </si>
+  <si>
+    <t>CONTEXT_ACCOUNT</t>
+  </si>
+  <si>
+    <t>CONTEXT_PLAYER</t>
   </si>
 </sst>
 </file>
@@ -2564,7 +2579,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39863D74-8F6A-4DBA-9900-ED18DEBD4CDC}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.42578125" customWidth="1"/>
@@ -2706,6 +2721,50 @@
         <v>30000</v>
       </c>
     </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>109</v>
+      </c>
+      <c r="B13" t="s">
+        <v>110</v>
+      </c>
+      <c r="C13">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>109</v>
+      </c>
+      <c r="B14" t="s">
+        <v>111</v>
+      </c>
+      <c r="C14">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>109</v>
+      </c>
+      <c r="B15" t="s">
+        <v>112</v>
+      </c>
+      <c r="C15">
+        <v>30001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>109</v>
+      </c>
+      <c r="B16" t="s">
+        <v>113</v>
+      </c>
+      <c r="C16">
+        <v>30002</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
